--- a/output/pdf_financials_xlsx/MPV.P.xlsx
+++ b/output/pdf_financials_xlsx/MPV.P.xlsx
@@ -57,11 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -503,11 +502,15 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>2.6965</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>2.896208</v>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -584,11 +587,15 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0.011329</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0.000645</v>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -767,11 +774,15 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>-0.048481</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>-0.690684</v>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -780,11 +791,15 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>48.526926</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>43.251706</v>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -953,11 +968,15 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>1.419825</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>0.037137</v>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1442,11 +1461,15 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
-        <v>424.174459</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>479.672325</v>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1455,11 +1478,15 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
-        <v>1.679658</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>1.927561</v>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1842,11 +1869,15 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
-        <v>304.400285</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>342.408416</v>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -1889,11 +1920,15 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
-        <v>50.053442</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>68.59980299999999</v>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -1987,11 +2022,15 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="3" t="n">
-        <v>119.774174</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>137.263909</v>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -2000,11 +2039,15 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="3" t="n">
-        <v>0.2823700754693483</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>0.2861618272432123</v>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2654,7 +2697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2664,32 +2707,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Line item (as printed)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Canonical key</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2739,11 +2782,7 @@
           <t>Goodwill 16 127,795,391 129,142,845 - - Trade and other payables 26 4,424,711 2,179,797</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AccountsPayable</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -2772,10 +2811,10 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>268.062981</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>270.20144</v>
       </c>
     </row>
@@ -2796,10 +2835,10 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -2848,10 +2887,10 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="4" t="n">
         <v>1.16706</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.799129</v>
       </c>
     </row>
@@ -2900,10 +2939,10 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>286.730041</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>276.500569</v>
       </c>
     </row>
@@ -2923,15 +2962,11 @@
           <t>Other investments 22 149,977 149,977 - - Total liabilities 924,404,002 878,493,305</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="4" t="n">
         <v>304.400285</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>342.408416</v>
       </c>
     </row>
@@ -2952,10 +2987,10 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="4" t="n">
         <v>119.774174</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="4" t="n">
         <v>137.263909</v>
       </c>
     </row>
@@ -2976,10 +3011,10 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="4" t="n">
         <v>16.289723</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="4" t="n">
         <v>70.07401900000001</v>
       </c>
     </row>
@@ -2999,15 +3034,11 @@
           <t>Trade and other receivables 24 3,083,722 3,694,684 - - Share capital 33 69,400,000 69,400,000</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" s="4" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="4" t="n">
         <v>69.40000000000001</v>
       </c>
     </row>
@@ -3028,10 +3059,10 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.320732</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="4" t="n">
         <v>-0.735894</v>
       </c>
     </row>
@@ -3051,15 +3082,11 @@
           <t>Restricted cash 35 961,153 1,250,923 - - Retained earnings 174,730,012 157,124,727</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" s="4" t="n">
         <v>50.053442</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="4" t="n">
         <v>68.59980299999999</v>
       </c>
     </row>
@@ -3076,14 +3103,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1,016,258,837 935,089,215</t>
+          <t>ASSETS AND LIABILITIES Non-current liabilities total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="4" t="n">
         <v>402.031682</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="4" t="n">
         <v>464.224841</v>
       </c>
     </row>
@@ -3104,10 +3131,10 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="4" t="n">
         <v>119.774174</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="4" t="n">
         <v>137.263909</v>
       </c>
     </row>
@@ -3127,11 +3154,7 @@
           <t>Inventories 23 38,663,060 34,248,377 - - Non-controlling interests 22 16,990,614 27,119,337</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MinorityInterest</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3159,15 +3182,11 @@
           <t>Non-current assets held for sale 38 38,797,431 42,875,148 - - Total equity 297,338,705 280,753,429</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" s="4" t="n">
         <v>119.774174</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="4" t="n">
         <v>137.263909</v>
       </c>
     </row>
@@ -3188,10 +3207,10 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="4" t="n">
         <v>17.065122</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="4" t="n">
         <v>11.680294</v>
       </c>
     </row>
@@ -3267,15 +3286,11 @@
           <t>Cash and cash equivalents 35 59,742,307 71,770,579</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="4" t="n">
         <v>1.419825</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="4" t="n">
         <v>0.037137</v>
       </c>
     </row>
@@ -3296,10 +3311,10 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="4" t="n">
         <v>3.302458</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="4" t="n">
         <v>3.087034</v>
       </c>
     </row>
@@ -3339,20 +3354,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>Archibald Anderson Bethel Annabel Hili</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>205,483,870 224,157,519</t>
+          <t>Total assets 1,221,742,707 1,159,246,734</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>22.142777</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>15.447484</v>
+      <c r="E26" s="4" t="n">
+        <v>424.174459</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>479.672325</v>
       </c>
     </row>
     <row r="27">
@@ -3363,24 +3378,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Archibald Anderson Bethel Annabel Hili</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Total assets 1,221,742,707 1,159,246,734</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>424.174459</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>479.672325</v>
+          <t>Trade and other payables 26 159,463,902 158,525,720</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="4" t="n">
+        <v>1.679658</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1.927561</v>
       </c>
     </row>
     <row r="28">
@@ -3396,19 +3407,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trade and other payables 26 159,463,902 158,525,720</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>AccountsPayable</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1.679658</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>1.927561</v>
+          <t>Contract liabilities 30 1,975,296 2,313,611</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -3424,7 +3435,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Contract liabilities 30 1,975,296 2,313,611</t>
+          <t>Debt securities in issue 32 64,997,847 37,125,153</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3452,7 +3463,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Debt securities in issue 32 64,997,847 37,125,153</t>
+          <t>Liabilities associated with assets held for sale 38 1,545,119 13,871,677</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3480,23 +3491,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liabilities associated with assets held for sale 38 1,545,119 13,871,677</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>AssetsHeldForSale</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other financial liabilities 28 - 2,000,000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="4" t="n">
+        <v>9.646661</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>15.359159</v>
       </c>
     </row>
     <row r="32">
@@ -3512,15 +3515,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Other financial liabilities 28 - 2,000,000</t>
+          <t>Bank loans and overdrafts 27 73,928,364 41,021,877</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>9.646661</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>15.359159</v>
+      <c r="E32" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>48.256339</v>
       </c>
     </row>
     <row r="33">
@@ -3536,15 +3539,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bank loans and overdrafts 27 73,928,364 41,021,877</t>
+          <t>Lease liabilities 20 16,495,631 15,643,327</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>48.256339</v>
+      <c r="E33" s="4" t="n">
+        <v>0.343925</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.364788</v>
       </c>
     </row>
     <row r="34">
@@ -3560,15 +3563,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lease liabilities 20 16,495,631 15,643,327</t>
+          <t>Current tax liability 6,270,621 4,882,657</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>0.343925</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.364788</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3584,43 +3591,39 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Current tax liability 6,270,621 4,882,657</t>
+          <t>Current liabilities total</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="4" t="n">
+        <v>17.670244</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>65.907847</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>NOTES € € € €</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>324,676,780 275,384,022</t>
+          <t>(Cap. 386) to prepare financial statements in accordance with accounting records are kept which disclose with reasonable Revenue 5 1,171,616,013 1,088,450,038</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" s="5" t="n">
-        <v>17.670244</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>65.907847</v>
+      <c r="E36" s="4" t="n">
+        <v>2.6965</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>2.896208</v>
       </c>
     </row>
     <row r="37">
@@ -3636,15 +3639,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(Cap. 386) to prepare financial statements in accordance with accounting records are kept which disclose with reasonable Revenue 5 1,171,616,013 1,088,450,038</t>
+          <t>International Financial Reporting Standards as adopted by the accuracy at any time the financial position of the Company Cost of sales 11 (937,594,365) (868,733,897)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>2.6965</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>2.896208</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3660,19 +3667,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>International Financial Reporting Standards as adopted by the accuracy at any time the financial position of the Company Cost of sales 11 (937,594,365) (868,733,897)</t>
+          <t>EU which give a true and fair view of the state of affairs of the and the Group which enable the Directors to ensure that the Gross profit 234,021,648 219,716,141</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="4" t="n">
+        <v>2.6965</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2.896208</v>
       </c>
     </row>
     <row r="39">
@@ -3688,19 +3691,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EU which give a true and fair view of the state of affairs of the and the Group which enable the Directors to ensure that the Gross profit 234,021,648 219,716,141</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>2.6965</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>2.896208</v>
+          <t>Company and the Group at the end of each financial period and financial statements comply with the Maltese Companies Act Other operating income 6 3,453,715 2,083,649</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="4" t="n">
+        <v>0.011329</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.000645</v>
       </c>
     </row>
     <row r="40">
@@ -3716,19 +3715,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Company and the Group at the end of each financial period and financial statements comply with the Maltese Companies Act Other operating income 6 3,453,715 2,083,649</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>0.011329</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.000645</v>
+          <t>of its profit or loss of the Company and its Group for the year then (Cap. 386). This responsibility includes designing, implementing Other operating expenses (351,742) (188,971)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -3744,19 +3743,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>of its profit or loss of the Company and its Group for the year then (Cap. 386). This responsibility includes designing, implementing Other operating expenses (351,742) (188,971)</t>
+          <t>ended. In preparing the financial statements, the Directors should: and maintaining such internal control as the Directors determine Selling expenses 11 (61,488,215) (54,743,697)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="4" t="n">
+        <v>-0.05149</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>-0.058626</v>
       </c>
     </row>
     <row r="42">
@@ -3772,15 +3767,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ended. In preparing the financial statements, the Directors should: and maintaining such internal control as the Directors determine Selling expenses 11 (61,488,215) (54,743,697)</t>
+          <t>is necessary to enable the preparation of financial statements Administrative expenses 11 (82,231,994) (74,226,360)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>-0.05149</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>-0.058626</v>
+      <c r="E42" s="4" t="n">
+        <v>-5.635434</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>-6.912436</v>
       </c>
     </row>
     <row r="43">
@@ -3796,15 +3791,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>is necessary to enable the preparation of financial statements Administrative expenses 11 (82,231,994) (74,226,360)</t>
+          <t>• select suitable accounting policies and apply them that are free from material misstatement, whether due to fraud Operating profit/(loss) 93,403,412 92,640,762</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>-5.635434</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>-6.912436</v>
+      <c r="E43" s="4" t="n">
+        <v>-2.979095</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>-4.074209</v>
       </c>
     </row>
     <row r="44">
@@ -3820,15 +3815,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>• select suitable accounting policies and apply them that are free from material misstatement, whether due to fraud Operating profit/(loss) 93,403,412 92,640,762</t>
+          <t>consistently; or error. The Directors are also responsible for safeguarding the Gain on bargain purchase 36 – 17,012,781</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>-2.979095</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>-4.074209</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3844,7 +3843,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>consistently; or error. The Directors are also responsible for safeguarding the Gain on bargain purchase 36 – 17,012,781</t>
+          <t>• make judgements and estimates that are reasonable and assets of the Company and the Group and hence for taking Other non-operating expenses 10 (6,040,545) –</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -3872,19 +3871,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>• make judgements and estimates that are reasonable and assets of the Company and the Group and hence for taking Other non-operating expenses 10 (6,040,545) –</t>
+          <t>prudent; reasonable steps for the prevention and detection of fraud and Investment income 7 16,339,356 6,400,800</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="4" t="n">
+        <v>65.61799999999999</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>62.375011</v>
       </c>
     </row>
     <row r="47">
@@ -3900,15 +3895,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>prudent; reasonable steps for the prevention and detection of fraud and Investment income 7 16,339,356 6,400,800</t>
+          <t>Investment losses 8 (1,108,844) (4,952,040)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>65.61799999999999</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>62.375011</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3919,24 +3918,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>other irregularities.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Investment losses 8 (1,108,844) (4,952,040)</t>
+          <t>• prepare the financial statements on a going concern basis, Net investment income 15,230,512 1,448,760</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="4" t="n">
+        <v>65.61799999999999</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>62.375011</v>
       </c>
     </row>
     <row r="49">
@@ -3952,19 +3947,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>• prepare the financial statements on a going concern basis, Net investment income 15,230,512 1,448,760</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NetInvestmentIncome</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>65.61799999999999</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>62.375011</v>
+          <t>unless it is inappropriate to presume that the Company and Finance income 9 1,653,305 661,312</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3980,19 +3975,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>unless it is inappropriate to presume that the Company and Finance income 9 1,653,305 661,312</t>
+          <t>the Group and will continue in business as a going concern; Finance costs 9 (34,688,325) (31,331,921)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="4" t="n">
+        <v>-12.781588</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>-15.344492</v>
       </c>
     </row>
     <row r="51">
@@ -4008,14 +3999,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>the Group and will continue in business as a going concern; Finance costs 9 (34,688,325) (31,331,921)</t>
+          <t>Net finance costs (33,035,020) (30,670,609)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="4" t="n">
         <v>-12.781588</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="4" t="n">
         <v>-15.344492</v>
       </c>
     </row>
@@ -4032,15 +4023,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Net finance costs (33,035,020) (30,670,609)</t>
+          <t>Profit before tax 11 69,558,359 80,431,694</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>-12.781588</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>-15.344492</v>
+      <c r="E52" s="4" t="n">
+        <v>49.857317</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>42.95631</v>
       </c>
     </row>
     <row r="53">
@@ -4051,20 +4042,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>other irregularities.</t>
+          <t>period on accrual basis;</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Profit before tax 11 69,558,359 80,431,694</t>
+          <t>Income tax (expense) / credit 14 (19,294,787) (14,991,435)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>49.857317</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>42.95631</v>
+      <c r="E53" s="4" t="n">
+        <v>-1.330391</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.295396</v>
       </c>
     </row>
     <row r="54">
@@ -4080,15 +4071,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Income tax (expense) / credit 14 (19,294,787) (14,991,435)</t>
+          <t>• value separately the components of asset and liability items; Profit for the year 50,263,572 65,440,259</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>-1.330391</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.295396</v>
+      <c r="E54" s="4" t="n">
+        <v>48.526926</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>43.251706</v>
       </c>
     </row>
     <row r="55">
@@ -4099,24 +4090,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>period on accrual basis;</t>
+          <t>and Discontinued operations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>• value separately the components of asset and liability items; Profit for the year 50,263,572 65,440,259</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>48.526926</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>43.251706</v>
+          <t>• report comparative figures corresponding to those in the Loss for the year from discontinued operations 29 – (477,551)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4132,19 +4123,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>• report comparative figures corresponding to those in the Loss for the year from discontinued operations 29 – (477,551)</t>
+          <t>Total profit for the year 50,263,572 64,962,708</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="4" t="n">
+        <v>48.526926</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>43.251706</v>
       </c>
     </row>
     <row r="57">
@@ -4155,24 +4142,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>and Discontinued operations</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Total profit for the year 50,263,572 64,962,708</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>48.526926</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>43.251706</v>
+          <t>Revaluation on property, plant and equipment 13,475,644 2,845,034</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -4188,7 +4175,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Revaluation on property, plant and equipment 13,475,644 2,845,034</t>
+          <t>Deferred taxation on revaluation of property, plant and equipment (1,593,855) -</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4216,19 +4203,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Deferred taxation on revaluation of property, plant and equipment (1,593,855) -</t>
+          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 18,674 679,033</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="4" t="n">
+        <v>0.233828</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>-0.786683</v>
       </c>
     </row>
     <row r="60">
@@ -4244,15 +4227,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 18,674 679,033</t>
+          <t>Reversal of fair value upon disposal of financial assets at fair value through other comprehensive income 22 (352,128) (345,019)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.233828</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>-0.786683</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4268,19 +4255,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Reversal of fair value upon disposal of financial assets at fair value through other comprehensive income 22 (352,128) (345,019)</t>
+          <t>Other comprehensive expense total</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="4" t="n">
+        <v>0.233828</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>-0.786683</v>
       </c>
     </row>
     <row r="62">
@@ -4296,15 +4279,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11,548,335 3,179,048</t>
+          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 353,534 21,991</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.233828</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.786683</v>
+      <c r="E62" s="4" t="n">
+        <v>-0.018499</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.266786</v>
       </c>
     </row>
     <row r="63">
@@ -4320,15 +4303,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 353,534 21,991</t>
+          <t>Recycling of cumulative fair value changes on debt instruments at fair value through other comprehensive income 22 (348,395) (406,378)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>-0.018499</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.266786</v>
+      <c r="E63" s="4" t="n">
+        <v>-0.257157</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>-0.242074</v>
       </c>
     </row>
     <row r="64">
@@ -4344,15 +4327,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Recycling of cumulative fair value changes on debt instruments at fair value through other comprehensive income 22 (348,395) (406,378)</t>
+          <t>Exchange differences on translation of foreign operations (6,152,774) 4,094,671</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>-0.257157</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>-0.242074</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4368,19 +4355,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Exchange differences on translation of foreign operations (6,152,774) 4,094,671</t>
+          <t>Total other comprehensive Income / (expense) 5,400,700 6,889,332</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="4" t="n">
+        <v>-0.041828</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>-0.761971</v>
       </c>
     </row>
     <row r="66">
@@ -4396,15 +4379,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(6,147,635) 3,710,284</t>
+          <t>Total comprehensive income for the year 55,664,272 71,852,040</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>-0.275656</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.024712</v>
+      <c r="E66" s="4" t="n">
+        <v>48.485098</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>42.489735</v>
       </c>
     </row>
     <row r="67">
@@ -4415,20 +4398,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Profit attributable to</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Total other comprehensive Income / (expense) 5,400,700 6,889,332</t>
+          <t>Owners of the company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>-0.041828</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>-0.761971</v>
+      <c r="E67" s="4" t="n">
+        <v>64.914227</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>49.572888</v>
       </c>
     </row>
     <row r="68">
@@ -4439,20 +4422,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Profit attributable to</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year 55,664,272 71,852,040</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>48.485098</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>42.489735</v>
+      <c r="E68" s="4" t="n">
+        <v>0.048481</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.690684</v>
       </c>
     </row>
     <row r="69">
@@ -4468,15 +4451,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Owners of the company</t>
+          <t>Profit attributable to total</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>64.914227</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>49.572888</v>
+      <c r="E69" s="4" t="n">
+        <v>64.96270800000001</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>50.263572</v>
       </c>
     </row>
     <row r="70">
@@ -4487,24 +4470,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Profit attributable to</t>
+          <t>Total comprehensive income attributable to</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>-0.048481</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>-0.690684</v>
+          <t>Owners of the company</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="4" t="n">
+        <v>71.803749</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>54.967112</v>
       </c>
     </row>
     <row r="71">
@@ -4515,20 +4494,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Profit attributable to</t>
+          <t>Total comprehensive income attributable to</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Profit attributable to total</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>64.96270800000001</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>50.263572</v>
+      <c r="E71" s="4" t="n">
+        <v>0.048291</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0.69716</v>
       </c>
     </row>
     <row r="72">
@@ -4544,66 +4523,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Owners of the company</t>
+          <t>Total comprehensive income attributable to total</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>71.803749</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>54.967112</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>-0.048291</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>-0.69716</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to total</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
+      <c r="E72" s="4" t="n">
         <v>71.85204</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F72" s="4" t="n">
         <v>55.664272</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/MPV.P.xlsx
+++ b/output/pdf_financials_xlsx/MPV.P.xlsx
@@ -430,6 +430,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/MPV.P.xlsx
+++ b/output/pdf_financials_xlsx/MPV.P.xlsx
@@ -2702,7 +2702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities total</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ASSETS AND LIABILITIES Non-current liabilities</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Archibald Anderson Bethel Annabel Hili</t>
+          <t>ASSETS AND LIABILITIES                                                                                                                                Non-current liabilities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Total assets 1,221,742,707 1,159,246,734</t>
+          <t>Archibald Anderson Bethel Annabel Hili Total assets 1,221,742,707 1,159,246,734</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>prudent; reasonable steps for the prevention and detection of fraud and Investment income 7 16,339,356 6,400,800</t>
+          <t>• prepare the financial statements on a going concern basis, Net investment income 15,230,512 1,448,760</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NOTES € € € €</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Investment losses 8 (1,108,844) (4,952,040)</t>
+          <t>unless it is inappropriate to presume that the Company and Finance income 9 1,653,305 661,312</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3923,20 +3923,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>other irregularities.</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>• prepare the financial statements on a going concern basis, Net investment income 15,230,512 1,448,760</t>
+          <t>the Group and will continue in business as a going concern; Finance costs 9 (34,688,325) (31,331,921)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="4" t="n">
-        <v>65.61799999999999</v>
+        <v>-12.781588</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>62.375011</v>
+        <v>-15.344492</v>
       </c>
     </row>
     <row r="49">
@@ -3947,24 +3947,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>other irregularities.</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>unless it is inappropriate to presume that the Company and Finance income 9 1,653,305 661,312</t>
+          <t>Income tax (expense) / credit 14 (19,294,787) (14,991,435)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="4" t="n">
+        <v>-1.330391</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.295396</v>
       </c>
     </row>
     <row r="50">
@@ -3975,20 +3971,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>other irregularities.</t>
+          <t>NOTES              €              €              €              €</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>the Group and will continue in business as a going concern; Finance costs 9 (34,688,325) (31,331,921)</t>
+          <t>• value separately the components of asset and liability items; Profit for the year 50,263,572 65,440,259</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="4" t="n">
-        <v>-12.781588</v>
+        <v>48.526926</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-15.344492</v>
+        <v>43.251706</v>
       </c>
     </row>
     <row r="51">
@@ -3999,20 +3995,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>other irregularities.</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Net finance costs (33,035,020) (30,670,609)</t>
+          <t>Revaluation on property, plant and equipment 13,475,644 2,845,034</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" s="4" t="n">
-        <v>-12.781588</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>-15.344492</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -4023,20 +4023,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>other irregularities.</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Profit before tax 11 69,558,359 80,431,694</t>
+          <t>Deferred taxation on revaluation of property, plant and equipment (1,593,855) -</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="4" t="n">
-        <v>49.857317</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>42.95631</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4047,20 +4051,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>period on accrual basis;</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Income tax (expense) / credit 14 (19,294,787) (14,991,435)</t>
+          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 18,674 679,033</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="4" t="n">
-        <v>-1.330391</v>
+        <v>0.233828</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.295396</v>
+        <v>-0.786683</v>
       </c>
     </row>
     <row r="54">
@@ -4071,20 +4075,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>period on accrual basis;</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>• value separately the components of asset and liability items; Profit for the year 50,263,572 65,440,259</t>
+          <t>Reversal of fair value upon disposal of financial assets at fair value through other comprehensive income 22 (352,128) (345,019)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" s="4" t="n">
-        <v>48.526926</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>43.251706</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4095,24 +4103,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>and Discontinued operations</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>• report comparative figures corresponding to those in the Loss for the year from discontinued operations 29 – (477,551)</t>
+          <t>Other comprehensive expense total</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E55" s="4" t="n">
+        <v>0.233828</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>-0.786683</v>
       </c>
     </row>
     <row r="56">
@@ -4123,20 +4127,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>and Discontinued operations</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Total profit for the year 50,263,572 64,962,708</t>
+          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 353,534 21,991</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="4" t="n">
-        <v>48.526926</v>
+        <v>-0.018499</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>43.251706</v>
+        <v>0.266786</v>
       </c>
     </row>
     <row r="57">
@@ -4152,19 +4156,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Revaluation on property, plant and equipment 13,475,644 2,845,034</t>
+          <t>Recycling of cumulative fair value changes on debt instruments at fair value through other comprehensive income 22 (348,395) (406,378)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="4" t="n">
+        <v>-0.257157</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>-0.242074</v>
       </c>
     </row>
     <row r="58">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Deferred taxation on revaluation of property, plant and equipment (1,593,855) -</t>
+          <t>Exchange differences on translation of foreign operations (6,152,774) 4,094,671</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4208,15 +4208,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 18,674 679,033</t>
+          <t>Total other comprehensive Income / (expense) 5,400,700 6,889,332</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="4" t="n">
-        <v>0.233828</v>
+        <v>-0.041828</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>-0.786683</v>
+        <v>-0.761971</v>
       </c>
     </row>
     <row r="60">
@@ -4232,19 +4232,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Reversal of fair value upon disposal of financial assets at fair value through other comprehensive income 22 (352,128) (345,019)</t>
+          <t>Total comprehensive income for the year 55,664,272 71,852,040</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="4" t="n">
+        <v>48.485098</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>42.489735</v>
       </c>
     </row>
     <row r="61">
@@ -4255,20 +4251,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Profit attributable to</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Other comprehensive expense total</t>
+          <t>Owners of the company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="4" t="n">
-        <v>0.233828</v>
+        <v>64.914227</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>-0.786683</v>
+        <v>49.572888</v>
       </c>
     </row>
     <row r="62">
@@ -4279,20 +4275,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Profit attributable to</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Increase / (decrease) in fair value of financial asset investments at fair value through other comprehensive income 22 353,534 21,991</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="4" t="n">
-        <v>-0.018499</v>
+        <v>0.048481</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.266786</v>
+        <v>0.690684</v>
       </c>
     </row>
     <row r="63">
@@ -4303,20 +4299,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Profit attributable to</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Recycling of cumulative fair value changes on debt instruments at fair value through other comprehensive income 22 (348,395) (406,378)</t>
+          <t>Profit attributable to total</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="4" t="n">
-        <v>-0.257157</v>
+        <v>64.96270800000001</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>-0.242074</v>
+        <v>50.263572</v>
       </c>
     </row>
     <row r="64">
@@ -4327,24 +4323,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Total comprehensive income attributable to</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Exchange differences on translation of foreign operations (6,152,774) 4,094,671</t>
+          <t>Owners of the company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="4" t="n">
+        <v>71.803749</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>54.967112</v>
       </c>
     </row>
     <row r="65">
@@ -4355,20 +4347,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Total comprehensive income attributable to</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Total other comprehensive Income / (expense) 5,400,700 6,889,332</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="4" t="n">
-        <v>-0.041828</v>
+        <v>0.048291</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>-0.761971</v>
+        <v>0.69716</v>
       </c>
     </row>
     <row r="66">
@@ -4379,163 +4371,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Total comprehensive income attributable to</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year 55,664,272 71,852,040</t>
+          <t>Total comprehensive income attributable to total</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="4" t="n">
-        <v>48.485098</v>
+        <v>71.85204</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>42.489735</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Profit attributable to</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Owners of the company</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" s="4" t="n">
-        <v>64.914227</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>49.572888</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Profit attributable to</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" s="4" t="n">
-        <v>0.048481</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>0.690684</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Profit attributable to</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Profit attributable to total</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" s="4" t="n">
-        <v>64.96270800000001</v>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>50.263572</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Owners of the company</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="4" t="n">
-        <v>71.803749</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>54.967112</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="4" t="n">
-        <v>0.048291</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>0.69716</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Total comprehensive income attributable to total</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="4" t="n">
-        <v>71.85204</v>
-      </c>
-      <c r="F72" s="4" t="n">
         <v>55.664272</v>
       </c>
     </row>
